--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheckthresh.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_recheckthresh.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,10 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,16 +149,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -783,23 +771,23 @@
       <c r="C4" s="3" t="n">
         <v>289.1</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="H4" s="11" t="n">
-        <v>10.8</v>
+      <c r="H4" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>1.2</v>
@@ -807,25 +795,25 @@
       <c r="K4" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M4" s="13" t="n">
-        <v>1.5</v>
+      <c r="M4" s="8" t="n">
+        <v>15.9</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="R4" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="R4" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -837,10 +825,10 @@
       <c r="U4" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V4" s="11" t="n">
+      <c r="V4" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>17</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -850,7 +838,7 @@
         <v>93</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -868,19 +856,19 @@
       <c r="C5" s="3" t="n">
         <v>464.5</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="I5" s="3" t="n">
@@ -895,26 +883,26 @@
       <c r="L5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="8" t="n">
         <v>13.9</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>98.8</v>
+        <v>98</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q5" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="R5" s="11" t="n">
+      <c r="R5" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>81</v>
@@ -922,10 +910,10 @@
       <c r="U5" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -935,7 +923,7 @@
         <v>76</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -953,19 +941,19 @@
       <c r="C6" s="3" t="n">
         <v>338</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H6" s="11" t="n">
+      <c r="G6" s="8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I6" s="3" t="n">
@@ -975,13 +963,13 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M6" s="13" t="n">
-        <v>94.2</v>
+      <c r="M6" s="8" t="n">
+        <v>14.2</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>16.1</v>
@@ -990,29 +978,29 @@
         <v>99</v>
       </c>
       <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>62.5</v>
+        <v>67.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>29</v>
+        <v>20.2</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>76</v>
@@ -1036,16 +1024,16 @@
       <c r="C7" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1063,23 +1051,23 @@
       <c r="L7" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.8</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q7" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>12.2</v>
+      <c r="R7" s="8" t="n">
+        <v>17.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>18</v>
@@ -1090,20 +1078,20 @@
       <c r="U7" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>17</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>15.3</v>
+        <v>18.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>8.4</v>
+        <v>84</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>33.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1121,17 +1109,17 @@
       <c r="C8" s="3" t="n">
         <v>377.9</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>90.59999999999999</v>
+      <c r="G8" s="8" t="n">
+        <v>9.6</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>14.2</v>
@@ -1140,7 +1128,7 @@
         <v>0.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>1.8</v>
@@ -1148,37 +1136,37 @@
       <c r="L8" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="M8" s="11" t="n">
-        <v>13.1</v>
+      <c r="M8" s="8" t="n">
+        <v>15.1</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>17.1</v>
+        <v>171.9</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>9.9</v>
+        <v>99</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R8" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="R8" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1204,18 +1192,18 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>1825.2</v>
+      </c>
+      <c r="D9" s="8" t="n">
         <v>126.5</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>71.5</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>55</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1225,52 +1213,52 @@
         <v>6.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="K9" s="12" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K9" s="9" t="n">
         <v>28.9</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" s="9" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="M9" s="8" t="n">
         <v>74.3</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>95.3</v>
+        <v>493</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q9" s="12" t="n">
+      <c r="Q9" s="8" t="n">
         <v>103.3</v>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="R9" s="8" t="n">
         <v>89.90000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>198.6</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>891.8</v>
+        <v>2.8</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V9" s="12" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="W9" s="9" t="n">
+      <c r="V9" s="8" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="W9" s="8" t="n">
         <v>87.2</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9429</v>
+        <v>429</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>16.1</v>
@@ -1291,16 +1279,16 @@
       <c r="C10" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>11</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1310,30 +1298,30 @@
         <v>1.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L10" s="12" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L10" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="M10" s="12" t="n">
+      <c r="M10" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>28.6</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="R10" s="12" t="n">
+      <c r="R10" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1345,17 +1333,17 @@
       <c r="U10" s="3" t="n">
         <v>5.4</v>
       </c>
-      <c r="V10" s="12" t="n">
-        <v>191.4</v>
-      </c>
-      <c r="W10" s="9" t="n">
+      <c r="V10" s="8" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="W10" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>19</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>88.8</v>
+        <v>86.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>3.2</v>
@@ -1376,16 +1364,16 @@
       <c r="C11" s="3" t="n">
         <v>324.6</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="E11" s="13" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="E11" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>10.1</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -1397,17 +1385,17 @@
       <c r="J11" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="L11" s="9" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>13.6</v>
+      <c r="L11" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>99</v>
@@ -1415,35 +1403,35 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="13" t="n">
-        <v>2.3</v>
+      <c r="Q11" s="8" t="n">
+        <v>22.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>1220.4</v>
+        <v>72</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V11" s="13" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="W11" s="9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W11" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>18.9</v>
+        <v>16.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>93.8</v>
+        <v>95</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1461,46 +1449,46 @@
       <c r="C12" s="3" t="n">
         <v>511.1</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L12" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M12" s="11" t="n">
-        <v>24.4</v>
+      <c r="L12" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>16.9</v>
+        <v>16.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q12" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1510,25 +1498,25 @@
         <v>16.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>281</v>
+        <v>85</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1546,13 +1534,13 @@
       <c r="C13" s="3" t="n">
         <v>455.6</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -1562,7 +1550,7 @@
         <v>8.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.8</v>
@@ -1570,22 +1558,22 @@
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M13" s="3" t="n">
+      <c r="L13" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M13" s="8" t="n">
         <v>11.6</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q13" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1595,22 +1583,22 @@
         <v>19.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>1866.8</v>
+        <v>66.8</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>726</v>
+        <v>26</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6</v>
@@ -1629,25 +1617,25 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>331.9</v>
-      </c>
-      <c r="D14" s="9" t="n">
+        <v>531.1</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>8.9</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>3.6</v>
@@ -1655,22 +1643,22 @@
       <c r="K14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>12.7</v>
+      <c r="M14" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q14" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q14" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1685,17 +1673,17 @@
       <c r="U14" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>29.3</v>
+        <v>20.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>8.4</v>
+        <v>84</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>4</v>
@@ -1716,46 +1704,46 @@
       <c r="C15" s="3" t="n">
         <v>484.5</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="F15" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>22.6</v>
+      <c r="F15" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>12.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>10.9</v>
+        <v>21.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M15" s="11" t="n">
-        <v>14.9</v>
+      <c r="M15" s="8" t="n">
+        <v>14.1</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="8" t="n">
         <v>25.7</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1770,17 +1758,17 @@
       <c r="U15" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>84.8</v>
+        <v>84</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>3.6</v>
@@ -1799,19 +1787,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2306.9</v>
-      </c>
-      <c r="D16" s="9" t="n">
+        <v>230.6</v>
+      </c>
+      <c r="D16" s="8" t="n">
         <v>127.2</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="8" t="n">
         <v>65.2</v>
       </c>
-      <c r="F16" s="12" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>16.2</v>
+      <c r="F16" s="8" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>62</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>48.9</v>
@@ -1820,29 +1808,29 @@
         <v>9.699999999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="K16" s="12" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K16" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="L16" s="9" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="M16" s="8" t="n">
         <v>66.2</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>45.6</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>432</v>
+        <v>493</v>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="12" t="n">
-        <v>115.7</v>
-      </c>
-      <c r="R16" s="12" t="n">
-        <v>92.90000000000001</v>
+      <c r="Q16" s="8" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>91.59999999999999</v>
@@ -1851,22 +1839,22 @@
         <v>313</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>255.8</v>
-      </c>
-      <c r="V16" s="12" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="V16" s="8" t="n">
         <v>100.4</v>
       </c>
-      <c r="W16" s="12" t="n">
-        <v>190.9</v>
+      <c r="W16" s="8" t="n">
+        <v>90.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>921</v>
+        <v>424</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>118.4</v>
+        <v>18.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1884,17 +1872,17 @@
       <c r="C17" s="3" t="n">
         <v>461.4</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F17" s="9" t="n">
+      <c r="E17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F17" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="G17" s="13" t="n">
-        <v>11.2</v>
+      <c r="G17" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>9.800000000000001</v>
@@ -1905,13 +1893,13 @@
       <c r="J17" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="K17" s="11" t="n">
-        <v>11.7</v>
+      <c r="K17" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M17" s="12" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M17" s="8" t="n">
         <v>13.2</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1923,10 +1911,10 @@
       <c r="P17" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="12" t="n">
+      <c r="Q17" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="R17" s="12" t="n">
+      <c r="R17" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1935,13 +1923,13 @@
       <c r="T17" s="3" t="n">
         <v>62.6</v>
       </c>
-      <c r="U17" s="11" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="V17" s="12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W17" s="9" t="n">
+      <c r="U17" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="W17" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1969,16 +1957,16 @@
       <c r="C18" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>9.6</v>
       </c>
       <c r="H18" s="3" t="n">
@@ -1990,43 +1978,43 @@
       <c r="J18" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>19.2</v>
+      <c r="L18" s="8" t="n">
+        <v>14.2</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>14</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q18" s="11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="R18" s="9" t="n">
+      <c r="Q18" s="8" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R18" s="8" t="n">
         <v>19</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V18" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2052,40 +2040,40 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>435.6</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E19" s="9" t="n">
+        <v>2135.6</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E19" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F19" s="9" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="G19" s="9" t="n">
+      <c r="F19" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G19" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L19" s="3" t="n">
+      <c r="K19" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="M19" s="11" t="n">
-        <v>11.8</v>
+      <c r="M19" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>12.6</v>
+        <v>18.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>47</v>
@@ -2093,14 +2081,14 @@
       <c r="P19" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q19" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="R19" s="9" t="n">
+      <c r="Q19" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="R19" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="S19" s="11" t="n">
-        <v>79.40000000000001</v>
+      <c r="S19" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>36.1</v>
@@ -2108,10 +2096,10 @@
       <c r="U19" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V19" s="11" t="n">
+      <c r="V19" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>17.5</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2137,18 +2125,18 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1417.9</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="F20" s="9" t="n">
+        <v>417.9</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2160,17 +2148,17 @@
       <c r="J20" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="8" t="n">
         <v>12.6</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>184.4</v>
@@ -2178,32 +2166,32 @@
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q20" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="R20" s="9" t="n">
+      <c r="Q20" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="R20" s="8" t="n">
         <v>17.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="W20" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="W20" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>2.9</v>
@@ -2222,18 +2210,18 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>379.3</v>
-      </c>
-      <c r="D21" s="9" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="E21" s="9" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F21" s="9" t="n">
+      <c r="E21" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>11.6</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2243,30 +2231,30 @@
         <v>1.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="L21" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="L21" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2278,20 +2266,20 @@
       <c r="U21" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>918.1</v>
+        <v>98</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>8.4</v>
+        <v>0.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2309,16 +2297,16 @@
       <c r="C22" s="3" t="n">
         <v>508.9</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F22" s="9" t="n">
+      <c r="E22" s="8" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F22" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>12.7</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2330,43 +2318,43 @@
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="L22" s="13" t="n">
-        <v>1.3</v>
+      <c r="K22" s="8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>13.2</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>14.4</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>297</v>
+        <v>97</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>59.8</v>
+        <v>59</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V22" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>18</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2394,16 +2382,16 @@
       <c r="C23" s="3" t="n">
         <v>2089.4</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>128.2</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>66.8</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>97.5</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>61.4</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2413,15 +2401,15 @@
         <v>1.3</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="K23" s="12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K23" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="L23" s="12" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="M23" s="12" t="n">
+      <c r="L23" s="8" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="M23" s="9" t="n">
         <v>69.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2431,35 +2419,35 @@
         <v>489</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="Q23" s="12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" s="8" t="n">
         <v>115.6</v>
       </c>
-      <c r="R23" s="12" t="n">
-        <v>191.5</v>
+      <c r="R23" s="8" t="n">
+        <v>91.5</v>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>232.8</v>
+        <v>328</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>149.8</v>
-      </c>
-      <c r="V23" s="12" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="V23" s="8" t="n">
         <v>94.3</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="n">
         <v>86.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>93</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>429.8</v>
+        <v>429</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2477,36 +2465,38 @@
       <c r="C24" s="3" t="n">
         <v>417.9</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="G24" s="11" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="H24" s="11" t="n">
+      <c r="G24" s="8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="12" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M24" s="12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="M24" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.7</v>
+        <v>26.2</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.8</v>
@@ -2514,25 +2504,25 @@
       <c r="P24" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>15.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V24" s="12" t="n">
+      <c r="V24" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2542,7 +2532,7 @@
         <v>85.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2560,19 +2550,19 @@
       <c r="C25" s="3" t="n">
         <v>233.6</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>7.6</v>
       </c>
-      <c r="H25" s="11" t="n">
+      <c r="H25" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I25" s="3" t="n">
@@ -2581,17 +2571,17 @@
       <c r="J25" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L25" s="11" t="n">
+      <c r="K25" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L25" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>19.8</v>
+      <c r="M25" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
@@ -2599,10 +2589,10 @@
       <c r="P25" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q25" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R25" s="3" t="n">
+      <c r="Q25" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="R25" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2614,17 +2604,17 @@
       <c r="U25" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="V25" s="11" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W25" s="9" t="n">
+      <c r="V25" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="W25" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>1</v>
@@ -2643,22 +2633,22 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>228.3</v>
-      </c>
-      <c r="D26" s="9" t="n">
+        <v>268.3</v>
+      </c>
+      <c r="D26" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G26" s="9" t="n">
-        <v>7.1</v>
+      <c r="G26" s="3" t="n">
+        <v>71.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.7</v>
@@ -2666,35 +2656,35 @@
       <c r="J26" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="M26" s="11" t="n">
+      <c r="M26" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>18.2</v>
+        <v>12.2</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="S26" s="11" t="n">
+      <c r="R26" s="8" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S26" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>1.6</v>
@@ -2702,7 +2692,7 @@
       <c r="V26" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="W26" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="X26" s="3" t="inlineStr"/>
@@ -2726,38 +2716,38 @@
       <c r="C27" s="3" t="n">
         <v>435.6</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G27" s="11" t="n">
-        <v>12.2</v>
+      <c r="G27" s="8" t="n">
+        <v>11.2</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>1.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="8" t="n">
         <v>13.2</v>
       </c>
-      <c r="L27" s="13" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>15.4</v>
+      <c r="L27" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>13.4</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>99</v>
@@ -2765,29 +2755,29 @@
       <c r="P27" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>28.1</v>
+        <v>20.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>88</v>
@@ -2811,16 +2801,16 @@
       <c r="C28" s="3" t="n">
         <v>331.3</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>9.9</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2830,45 +2820,45 @@
         <v>0.7</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K28" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K28" s="8" t="n">
         <v>32.8</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="8" t="n">
         <v>14.3</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>16.2</v>
+        <v>12.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" s="8" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>11.9</v>
+        <v>16.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>48.1</v>
+        <v>18</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2894,21 +2884,21 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>309.7</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="F29" s="9" t="n">
+        <v>309.1</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F29" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="H29" s="11" t="n">
+      <c r="H29" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="I29" s="3" t="n">
@@ -2917,50 +2907,50 @@
       <c r="J29" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L29" s="11" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M29" s="11" t="n">
+      <c r="K29" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M29" s="8" t="n">
         <v>15</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="R29" s="11" t="n">
+      <c r="R29" s="8" t="n">
         <v>19</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1.1</v>
+        <v>19.1</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>6.6</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="V29" s="11" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="W29" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X29" s="11" t="n">
+      <c r="V29" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X29" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>0.6</v>
@@ -2979,18 +2969,18 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="E30" s="9" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="8" t="n">
         <v>94.3</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="8" t="n">
         <v>44.9</v>
       </c>
       <c r="H30" s="3" t="n">
@@ -3002,26 +2992,26 @@
       <c r="J30" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="K30" s="8" t="n">
         <v>76.90000000000001</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="L30" s="9" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="M30" s="8" t="n">
         <v>74.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>494.8</v>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="9" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="R30" s="12" t="n">
+      <c r="Q30" s="8" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="R30" s="8" t="n">
         <v>89.2</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3033,8 +3023,8 @@
       <c r="U30" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="V30" s="12" t="n">
-        <v>8.5</v>
+      <c r="V30" s="9" t="n">
+        <v>85.09999999999999</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>82.40000000000001</v>
@@ -3043,10 +3033,10 @@
         <v>92.09999999999999</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>9428</v>
+        <v>478</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3064,14 +3054,14 @@
       <c r="C31" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E31" s="9" t="n">
+      <c r="D31" s="13" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="E31" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="F31" s="9" t="n">
-        <v>18.9</v>
+      <c r="F31" s="13" t="n">
+        <v>118.9</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>90.40000000000001</v>
@@ -3086,38 +3076,38 @@
         <v>0.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="12" t="n">
+      <c r="L31" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="M31" s="12" t="n">
-        <v>14.9</v>
+      <c r="M31" s="9" t="n">
+        <v>149.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>60.4</v>
+        <v>22.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q31" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="Q31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="R31" s="12" t="n">
-        <v>87.8</v>
+      <c r="R31" s="8" t="n">
+        <v>17.8</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V31" s="12" t="n">
-        <v>17</v>
+        <v>14.4</v>
+      </c>
+      <c r="V31" s="9" t="n">
+        <v>170.4</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>16.3</v>
@@ -3129,7 +3119,7 @@
         <v>95</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3145,72 +3135,72 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>364.2</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="G32" s="3" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G32" s="8" t="n">
         <v>14.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="L32" s="13" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="M32" s="13" t="n">
-        <v>1.1</v>
+        <v>32.3</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q32" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="R32" s="11" t="n">
-        <v>19.5</v>
+      <c r="R32" s="8" t="n">
+        <v>14.8</v>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="W32" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>1.2</v>
+        <v>12.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>8.6</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3228,19 +3218,19 @@
       <c r="C33" s="3" t="n">
         <v>411.2</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H33" s="11" t="n">
+      <c r="H33" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="I33" s="3" t="n">
@@ -3252,14 +3242,14 @@
       <c r="K33" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="L33" s="3" t="n">
-        <v>14.5</v>
+      <c r="L33" s="8" t="n">
+        <v>14.3</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="N33" s="11" t="n">
-        <v>9161.9</v>
+      <c r="N33" s="3" t="n">
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3267,35 +3257,35 @@
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>1.9</v>
+        <v>19.6</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>71.8</v>
+        <v>77.8</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V33" s="9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>2880.9</v>
+        <v>88</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3313,17 +3303,17 @@
       <c r="C34" s="3" t="n">
         <v>211.4</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="E34" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F34" s="3" t="n">
+      <c r="E34" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F34" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="G34" s="3" t="n">
-        <v>14.6</v>
+      <c r="G34" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>14.2</v>
@@ -3335,52 +3325,52 @@
         <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
+      </c>
+      <c r="L34" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>115</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>17</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>29.1</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="R34" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="R34" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>97.5</v>
+        <v>17.3</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V34" s="9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="W34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W34" s="8" t="n">
         <v>15.2</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3398,16 +3388,16 @@
       <c r="C35" s="3" t="n">
         <v>477.8</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="E35" s="9" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F35" s="9" t="n">
+      <c r="E35" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3422,10 +3412,10 @@
       <c r="K35" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M35" s="11" t="n">
+      <c r="M35" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3437,25 +3427,25 @@
       <c r="P35" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q35" s="11" t="n">
+      <c r="Q35" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>18.3</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>11.9</v>
+        <v>27.9</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>60.8</v>
+        <v>60</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="W35" s="9" t="n">
+      <c r="V35" s="8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W35" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3465,7 +3455,7 @@
         <v>84</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>128.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3483,20 +3473,20 @@
       <c r="C36" s="3" t="n">
         <v>613.2</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>3.3</v>
@@ -3507,7 +3497,7 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="8" t="n">
         <v>15</v>
       </c>
       <c r="M36" s="3" t="n">
@@ -3517,40 +3507,40 @@
         <v>16.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q36" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="Q36" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="R36" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>32.1</v>
+        <v>54.1</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="V36" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V36" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>114.8</v>
+        <v>71.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3566,73 +3556,73 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2078.2</v>
-      </c>
-      <c r="D37" s="12" t="n">
+        <v>207.8</v>
+      </c>
+      <c r="D37" s="8" t="n">
         <v>118.4</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="8" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>292.2</v>
-      </c>
-      <c r="G37" s="13" t="n">
-        <v>35.2</v>
+      <c r="F37" s="8" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>32.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>56.7</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="K37" s="12" t="n">
-        <v>507.9</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>68.59999999999999</v>
+      <c r="K37" s="9" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>11.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Q37" s="12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>101</v>
       </c>
-      <c r="R37" s="12" t="n">
-        <v>59.9</v>
+      <c r="R37" s="8" t="n">
+        <v>84.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>380.9</v>
+        <v>3809.1</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="V37" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="W37" s="9" t="n">
+      <c r="V37" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="W37" s="8" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>429.8</v>
+        <v>429.5</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3651,50 +3641,50 @@
       <c r="C38" s="3" t="n">
         <v>415.6</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="H38" s="11" t="n">
+      <c r="H38" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="I38" s="11" t="n">
-        <v>17</v>
+      <c r="I38" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="M38" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Q38" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="R38" s="12" t="n">
-        <v>97</v>
+      <c r="R38" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>17.6</v>
@@ -3705,17 +3695,17 @@
       <c r="U38" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>16.3</v>
       </c>
-      <c r="X38" s="11" t="n">
+      <c r="X38" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>3.1</v>
@@ -3736,53 +3726,53 @@
       <c r="C39" s="3" t="n">
         <v>624.3</v>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E39" s="9" t="n">
+      <c r="D39" s="8" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E39" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="F39" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G39" s="3" t="n">
+      <c r="F39" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G39" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>7.6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="11" t="n">
+      <c r="L39" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>12.2</v>
+        <v>13.2</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q39" s="9" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>8.4</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R39" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>26</v>
@@ -3790,11 +3780,11 @@
       <c r="U39" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V39" s="13" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="W39" s="9" t="n">
-        <v>16.5</v>
+      <c r="V39" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W39" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>16.5</v>
@@ -3821,28 +3811,28 @@
       <c r="C40" s="3" t="n">
         <v>637.7</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="E40" s="9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="E40" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F40" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="G40" s="11" t="n">
-        <v>65.3</v>
+      <c r="G40" s="8" t="n">
+        <v>16.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>15.3</v>
+        <v>5.3</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K40" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
@@ -3858,27 +3848,27 @@
         <v>98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q40" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q40" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>1948.8</v>
+        <v>48</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3906,67 +3896,67 @@
       <c r="C41" s="3" t="n">
         <v>644.3</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M41" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N41" s="11" t="n">
-        <v>18.8</v>
+        <v>10.7</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>8.1</v>
+        <v>22.1</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>947</v>
+        <v>47</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="X41" s="11" t="n">
-        <v>88.8</v>
+      <c r="X41" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>239</v>
+        <v>59</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>16.8</v>
@@ -3987,49 +3977,49 @@
       <c r="C42" s="3" t="n">
         <v>608.8</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="E42" s="13" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="G42" s="3" t="n">
+      <c r="E42" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G42" s="8" t="n">
         <v>16.5</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>10</v>
+        <v>5.9</v>
+      </c>
+      <c r="K42" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="M42" s="11" t="n">
+      <c r="M42" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N42" s="11" t="n">
+      <c r="N42" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>18.2</v>
+        <v>98</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q42" s="9" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="R42" s="3" t="n">
+      <c r="Q42" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="R42" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -4037,16 +4027,16 @@
         <v>49</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V42" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="V42" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>61</v>
@@ -4070,16 +4060,16 @@
       <c r="C43" s="3" t="n">
         <v>604.4</v>
       </c>
-      <c r="D43" s="9" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="G43" s="9" t="n">
+      <c r="D43" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G43" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4089,55 +4079,55 @@
         <v>3.5</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>8</v>
+        <v>5.4</v>
+      </c>
+      <c r="K43" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M43" s="11" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N43" s="11" t="n">
-        <v>19.8</v>
+        <v>11.4</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>46.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>22.8</v>
+        <v>32.2</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="V43" s="11" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="W43" s="9" t="n">
+      <c r="V43" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W43" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="X43" s="11" t="n">
-        <v>120.9</v>
+      <c r="X43" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>239.2</v>
+        <v>29.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4155,26 +4145,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="15" t="inlineStr"/>
-      <c r="F44" s="15" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="15" t="inlineStr"/>
-      <c r="M44" s="15" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="12" t="inlineStr"/>
+      <c r="M44" s="12" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="15" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="15" t="inlineStr"/>
-      <c r="W44" s="9" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4194,74 +4184,74 @@
       <c r="C45" s="3" t="n">
         <v>3119.5</v>
       </c>
-      <c r="D45" s="9" t="n">
+      <c r="D45" s="8" t="n">
         <v>131.1</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="8" t="n">
         <v>53.9</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="8" t="n">
         <v>92.5</v>
       </c>
-      <c r="G45" s="9" t="n">
-        <v>77.2</v>
+      <c r="G45" s="3" t="n">
+        <v>77.5</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>181.9</v>
+        <v>18.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="K45" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L45" s="12" t="n">
+      <c r="K45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="n">
         <v>56.4</v>
       </c>
-      <c r="M45" s="12" t="n">
-        <v>155.9</v>
+      <c r="M45" s="9" t="n">
+        <v>55.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>161.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>9498</v>
+        <v>26</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q45" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" s="9" t="n">
         <v>126.3</v>
       </c>
-      <c r="R45" s="12" t="n">
+      <c r="R45" s="8" t="n">
         <v>89.2</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>81.8</v>
+        <v>81.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>282.5</v>
+        <v>252.5</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>79.8</v>
       </c>
-      <c r="V45" s="12" t="n">
+      <c r="V45" s="8" t="n">
         <v>108.9</v>
       </c>
-      <c r="W45" s="12" t="n">
+      <c r="W45" s="8" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>10688.8</v>
+        <v>60.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>2302.8</v>
+        <v>302.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>20.7</v>
+        <v>50.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4279,17 +4269,17 @@
       <c r="C46" s="3" t="n">
         <v>223.9</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E46" s="9" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F46" s="9" t="n">
+      <c r="E46" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F46" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G46" s="11" t="n">
-        <v>51.3</v>
+      <c r="G46" s="8" t="n">
+        <v>15.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.5</v>
@@ -4298,52 +4288,52 @@
         <v>3.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K46" s="11" t="n">
-        <v>1111.9</v>
-      </c>
-      <c r="L46" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M46" s="12" t="n">
+      <c r="M46" s="9" t="n">
         <v>11.1</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q46" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q46" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="R46" s="12" t="n">
+      <c r="R46" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>11.9</v>
+        <v>16.8</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="U46" s="11" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="V46" s="12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W46" s="9" t="n">
+      <c r="U46" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="V46" s="9" t="n">
+        <v>218.4</v>
+      </c>
+      <c r="W46" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>161.2</v>
+        <v>61.2</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>10.1</v>
